--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="R4087df16ae9a4403"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="Rd36b535119574ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="3" r:id="R4413560f98fa4ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="Rbf13e79b74c54fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R57d09b1f7c914e8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="3" r:id="R1785a83f10e04ef3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -171,9 +171,6 @@
     <x:t xml:space="preserve">CMS · Configuración</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Parámetros generales leídos por Python. Mantén la publicación de datos personales y enlaces privados en No para GitHub público.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Clave</x:t>
   </x:si>
   <x:si>
@@ -222,13 +219,13 @@
     <x:t xml:space="preserve">publishEvidenceLinks</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">publishPersonalData</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">No</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">No recomendado en repositorio público</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">publishPersonalData</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1410,7 +1407,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea68651e66ac47c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ed55fb931c84037"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2115,7 +2112,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a5763a19b274ef8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5f354fd7b9b4b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2137,18 +2134,18 @@
       <x:c r="C1" s="16"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="17" t="s">
-        <x:v>53</x:v>
+      <x:c r="A2" s="17" t="str">
+        <x:v>Parámetros generales leídos por Python. Los vínculos se publican sólo cuando usan HTTPS y un dominio autorizado.</x:v>
       </x:c>
       <x:c r="B2" s="17"/>
       <x:c r="C2" s="17"/>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>4</x:v>
@@ -2156,73 +2153,73 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B5" s="3" t="s">
+      <x:c r="C5" s="15" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="C5" s="15" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="s">
+      <x:c r="C6" s="15" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B7" s="3" t="s">
+      <x:c r="C7" s="15" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B10" s="3" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>Si</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="str">
+        <x:v>Publicar el vínculo directo validado tal como viene en el Excel</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
         <x:v>70</x:v>
@@ -2276,7 +2273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R771bede38e38496e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75c12d4a9cdf46f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A207D5A6-823F-4BAB-95BA-1D5D8AC97A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554A8993-1775-4FAF-8F66-B53BC3C29D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="88">
   <si>
     <t>CMS · Actividades y fechas</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Programacion Hornos Merry - Focaccia</t>
   </si>
   <si>
-    <t>Validación de programación y ejecución.</t>
-  </si>
-  <si>
     <t>Media</t>
   </si>
   <si>
@@ -293,6 +290,15 @@
   </si>
   <si>
     <t>Carga de Foto|Proyecto Starbucks</t>
+  </si>
+  <si>
+    <t>Community Board</t>
+  </si>
+  <si>
+    <t>Valida Actualizacion de Tiendas que aplique</t>
+  </si>
+  <si>
+    <t>Validación de programación|Hornos Turbo Chef no se Considera</t>
   </si>
 </sst>
 </file>
@@ -717,7 +723,7 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="3" max="3" width="65.25" customWidth="1"/>
     <col min="4" max="5" width="15" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
@@ -815,7 +821,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="D6" s="6">
         <v>46262</v>
@@ -830,7 +836,7 @@
         <v>13</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -842,10 +848,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="6">
         <v>46262</v>
@@ -860,7 +866,7 @@
         <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -872,10 +878,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="6">
         <v>46262</v>
@@ -890,7 +896,7 @@
         <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -902,10 +908,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" s="6">
         <v>46262</v>
@@ -932,10 +938,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" s="6">
         <v>46262</v>
@@ -950,7 +956,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -962,10 +968,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="D11" s="6">
         <v>46262</v>
@@ -980,7 +986,7 @@
         <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -992,10 +998,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="D12" s="6">
         <v>46262</v>
@@ -1013,19 +1019,37 @@
         <v>14</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="5"/>
+      <c r="A13" s="4">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E13" s="6">
+        <v>46268</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4"/>
@@ -2065,7 +2089,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2073,7 +2097,7 @@
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -2081,13 +2105,13 @@
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -2095,13 +2119,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -2109,13 +2133,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -2123,13 +2147,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -2137,13 +2161,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
@@ -2151,13 +2175,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
@@ -2165,13 +2189,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>13</v>
@@ -2770,24 +2794,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="34" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:3" ht="28" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
     </row>
     <row r="4" spans="1:3" ht="28" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -2795,112 +2819,112 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554A8993-1775-4FAF-8F66-B53BC3C29D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C7EA0E-7455-4F0E-9101-EEE6166BFF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="90">
   <si>
     <t>CMS · Actividades y fechas</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Roll Out</t>
   </si>
   <si>
-    <t>Seguimiento del despliegue o implementación operativa.</t>
-  </si>
-  <si>
     <t>Si</t>
   </si>
   <si>
@@ -283,12 +280,6 @@
     <t>Vigente</t>
   </si>
   <si>
-    <t>Colocacion de Materiales Customer Experience</t>
-  </si>
-  <si>
-    <t>Validación del estándar Max &amp; Min | Acomodo de Back</t>
-  </si>
-  <si>
     <t>Carga de Foto|Proyecto Starbucks</t>
   </si>
   <si>
@@ -298,7 +289,22 @@
     <t>Valida Actualizacion de Tiendas que aplique</t>
   </si>
   <si>
-    <t>Validación de programación|Hornos Turbo Chef no se Considera</t>
+    <t>Activacion PSL Sharpie</t>
+  </si>
+  <si>
+    <t>Validacion Roll Out</t>
+  </si>
+  <si>
+    <t>Programacion MerryChef</t>
+  </si>
+  <si>
+    <t>Colocacion de Materiales Stickers</t>
+  </si>
+  <si>
+    <t>Estándar Max &amp; Min | Acomodo de Back</t>
+  </si>
+  <si>
+    <t>Enfoque al Menos 2 Sharpies Naranja en Tienda</t>
   </si>
 </sst>
 </file>
@@ -791,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="D5" s="6">
         <v>46262</v>
@@ -800,13 +806,13 @@
         <v>46268</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="I5" s="5" t="str">
         <f t="shared" ref="I5:I11" ca="1" si="0">IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente"))</f>
@@ -818,10 +824,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" s="6">
         <v>46262</v>
@@ -830,13 +836,13 @@
         <v>46268</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -848,10 +854,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="D7" s="6">
         <v>46262</v>
@@ -860,13 +866,13 @@
         <v>46271</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I7" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -878,10 +884,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D8" s="6">
         <v>46262</v>
@@ -890,13 +896,13 @@
         <v>46268</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -908,10 +914,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D9" s="6">
         <v>46262</v>
@@ -920,13 +926,13 @@
         <v>46271</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="I9" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -938,10 +944,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D10" s="6">
         <v>46262</v>
@@ -950,13 +956,13 @@
         <v>46271</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -968,10 +974,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D11" s="6">
         <v>46262</v>
@@ -980,13 +986,13 @@
         <v>46278</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -998,10 +1004,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>80</v>
       </c>
       <c r="D12" s="6">
         <v>46262</v>
@@ -1010,16 +1016,16 @@
         <v>46271</v>
       </c>
       <c r="F12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="I12" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1027,10 +1033,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D13" s="6">
         <v>46262</v>
@@ -1039,28 +1045,46 @@
         <v>46268</v>
       </c>
       <c r="F13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="I13" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="6">
+        <v>46262</v>
+      </c>
+      <c r="E14" s="6">
+        <v>46265</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4"/>
@@ -2089,7 +2113,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2097,7 +2121,7 @@
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -2105,13 +2129,13 @@
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -2119,86 +2143,86 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4" hidden="1">
@@ -2794,24 +2818,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="34" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:3" ht="28" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
     </row>
     <row r="4" spans="1:3" ht="28" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -2819,112 +2843,112 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC47BD7-389D-4E6F-A713-E4998122970E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B9D98E-5C99-44E4-8E9F-88D188544107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -905,13 +905,13 @@
         <v>46268</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B9D98E-5C99-44E4-8E9F-88D188544107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADA2043-8C38-473B-BC05-2F35F33B54B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="91">
   <si>
     <t>CMS · Actividades y fechas</t>
   </si>
@@ -95,12 +95,6 @@
   </si>
   <si>
     <t>Instalación o seguimiento del rack FHW.</t>
-  </si>
-  <si>
-    <t>QR - Qualtrics</t>
-  </si>
-  <si>
-    <t>Colocacion de Materiales Stickers</t>
   </si>
   <si>
     <t>Max &amp; Min</t>
@@ -499,7 +493,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ActividadesCMS" displayName="ActividadesCMS" ref="A4:I104" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ActividadesCMS" displayName="ActividadesCMS" ref="A4:I103" totalsRowShown="0">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Orden"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Actividad"/>
@@ -733,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -824,7 +818,7 @@
         <v>14</v>
       </c>
       <c r="I5" s="5" t="str">
-        <f t="shared" ref="I5:I11" ca="1" si="0">IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente"))</f>
+        <f t="shared" ref="I5:I10" ca="1" si="0">IF(AND(D5&lt;&gt;"",TODAY()&lt;D5),"Programada",IF(AND(E5&lt;&gt;"",TODAY()&gt;E5),"Vencida","Vigente"))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -902,16 +896,16 @@
         <v>46262</v>
       </c>
       <c r="E8" s="6">
-        <v>46268</v>
+        <v>46271</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I8" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -941,7 +935,7 @@
         <v>13</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I9" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -953,16 +947,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>46262</v>
       </c>
       <c r="E10" s="6">
-        <v>46271</v>
+        <v>46278</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>13</v>
@@ -971,7 +965,7 @@
         <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I10" s="5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -992,7 +986,7 @@
         <v>46262</v>
       </c>
       <c r="E11" s="6">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>13</v>
@@ -1001,10 +995,10 @@
         <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I11" s="5" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF(AND(D11&lt;&gt;"",TODAY()&lt;D11),"Programada",IF(AND(E11&lt;&gt;"",TODAY()&gt;E11),"Vencida","Vigente"))</f>
         <v>Vigente</v>
       </c>
     </row>
@@ -1022,7 +1016,7 @@
         <v>46262</v>
       </c>
       <c r="E12" s="6">
-        <v>46271</v>
+        <v>46268</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>13</v>
@@ -1052,7 +1046,7 @@
         <v>46262</v>
       </c>
       <c r="E13" s="6">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>13</v>
@@ -1073,25 +1067,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D14" s="6">
         <v>46262</v>
       </c>
       <c r="E14" s="6">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14" s="5" t="str">
         <f ca="1">IF(AND(D14&lt;&gt;"",TODAY()&lt;D14),"Programada",IF(AND(E14&lt;&gt;"",TODAY()&gt;E14),"Vencida","Vigente"))</f>
@@ -1103,10 +1097,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" s="6">
         <v>46262</v>
@@ -1115,7 +1109,7 @@
         <v>46295</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>13</v>
@@ -1129,34 +1123,15 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="4">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="6">
-        <v>46262</v>
-      </c>
-      <c r="E16" s="6">
-        <v>46295</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="5" t="str">
-        <f ca="1">IF(AND(D16&lt;&gt;"",TODAY()&lt;D16),"Programada",IF(AND(E16&lt;&gt;"",TODAY()&gt;E16),"Vencida","Vigente"))</f>
-        <v>Vigente</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4"/>
@@ -2115,31 +2090,20 @@
       <c r="H103" s="4"/>
       <c r="I103" s="5"/>
     </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="5"/>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I104">
+  <conditionalFormatting sqref="I5:I103">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Vencida"/>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Vigente"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:G104" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="F5:G103" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Si,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H5:H104" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="H5:H103" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2163,7 +2127,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2171,7 +2135,7 @@
     </row>
     <row r="2" spans="1:4" ht="28" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -2179,13 +2143,13 @@
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -2193,13 +2157,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
@@ -2207,13 +2171,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>13</v>
@@ -2221,13 +2185,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
@@ -2235,13 +2199,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
@@ -2249,13 +2213,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
@@ -2263,13 +2227,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>13</v>
@@ -2868,24 +2832,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="34" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:3" ht="28" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
     </row>
     <row r="4" spans="1:3" ht="28" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -2893,112 +2857,112 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADA2043-8C38-473B-BC05-2F35F33B54B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FF0F3E-842D-4E57-B997-1D8351BDD1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1079,7 +1079,7 @@
         <v>46295</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>13</v>
@@ -1109,7 +1109,7 @@
         <v>46295</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>13</v>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,10 +8,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gerentes'!$A$4:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tiendas Abiertas'!$A$4:$E$361</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,7 +85,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -140,6 +142,11 @@
         <fgColor rgb="00E6F2ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F8F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -177,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,6 +215,10 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3033,6 +3044,12 @@
     <cfRule type="expression" priority="4" dxfId="2">
       <formula>E5="Pendiente"</formula>
     </cfRule>
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>E5="Pendiente"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2">
+      <formula>E5="Pendiente"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="F5:F104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3055,7 +3072,9717 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E361"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>CMS · Tiendas Abiertas</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Vista generada desde Directorio.xlsx. Sólo Estatus = Abierta alimenta tiendas, conteos y avance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>CC Nombre</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Estatus</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38481</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Alfonso Reyes</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>38415</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38108</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Campos Eliseos</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>38128</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Condesa</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38597</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38382</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Homero</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>38191</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Masarik Spencer</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>38627</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Moliere 222</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>38187</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Nuevo Leon DT</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>38220</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Obelisco</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>38522</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Rio Hudson</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>38110</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Torre Mayor</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>38541</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Torre Polanco</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Alberto Torrado Aguilar Cauz</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>38101</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>38433</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Bolsa Mexicana de Valores</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>38555</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Capital Reforma</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>38422</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Corporativo HSBC</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>43188</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Insurgentes Tehuantepec</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>38272</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>38654</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Reforma 180</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>38285</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Reforma 222</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>38291</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Reforma 222 II</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>38389</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Rio Marne</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>38681</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Torre Diana</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>38404</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Varsovia</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Guadalupe Ibarra Martínez</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>38194</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>38612</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Antara II</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>38399</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Carso Polanco I</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>38470</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Chapultepec Reforma</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>38118</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Corporativo Polanco</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>38405</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Ejercito Nacional</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>38219</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Irrigacion</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>38111</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Masarik</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>38676</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Miyana</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>38982</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Miyana II</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>38581</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>Parques BBVA</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>43045</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Periferico Polanco DT</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>38557</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Rio San Joaquin</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Torre BBVA</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>38349</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Torre Inverlat</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Luis Manuel Neri Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>38182</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>Aeropuerto D8</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>38167</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>Aeropuerto Dufry</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>38151</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>Aeropuerto II Sala Bravo</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>38171</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Aeropuerto Internacional II</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>38906</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>APTO Ciudad de MéxicoAMB PTA 2</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>38803</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>Apto T1 AMB Puerta 8</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>38796</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>Apto T1 AMB Sala J</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>38795</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>Apto T1 Pb N Pta 7</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>38344</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Parques Polanco</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>38635</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>Punto Polanco</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>38653</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>Salon Ejecutivo T1 AICM</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>38299</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>T2 Llegadas</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>38297</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>T2 Salida Internacional</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>38298</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>T2 Salida Nacional</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>38943</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>Terraza T2 Amb</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>38858</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>Torre de Pemex</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>Maria Anallely Sanchez Garcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>38483</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>Forum Buenavista</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>38554</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>Forum Buenavista II</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>38850</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>Hospital Angeles Clinica Londres</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>38440</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>Hospital Angeles Metropolitano</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr">
+        <is>
+          <t>38504</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>Insurgentes Wtc</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>38312</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>La Salle</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr">
+        <is>
+          <t>38498</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>Montecitos Wtc</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>38602</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>Obrero Mundial</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
+        <is>
+          <t>38173</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Delta Planta Alta</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr">
+        <is>
+          <t>38658</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Delta Planta Baja</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr">
+        <is>
+          <t>38432</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Luis Cabrera</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="19" t="inlineStr">
+        <is>
+          <t>38558</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>Roma Sur</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E72" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="inlineStr">
+        <is>
+          <t>38752</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>Star Medica Roma</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="19" t="inlineStr">
+        <is>
+          <t>38378</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>Torre Mexicana</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E74" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>38423</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>Torre Wtc</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E75" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>38556</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>Tuxpan 53</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E76" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>38109</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>Wtc</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>Nora Caracas Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>38155</t>
+        </is>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>16 de Septiembre</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr">
+        <is>
+          <t>38497</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>5 de Mayo</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr">
+        <is>
+          <t>38203</t>
+        </is>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>Embassy Suites</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr">
+        <is>
+          <t>38234</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>Fiesta Americana Reforma</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr">
+        <is>
+          <t>38465</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>Juarez 32</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr">
+        <is>
+          <t>38487</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>Madero</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr">
+        <is>
+          <t>38762</t>
+        </is>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>Patio Boturini</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr">
+        <is>
+          <t>38123</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Alameda</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr">
+        <is>
+          <t>43123</t>
+        </is>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Tlatelolco</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr">
+        <is>
+          <t>38376</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>Torre Caballito</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>38463</t>
+        </is>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="inlineStr">
+        <is>
+          <t>38785</t>
+        </is>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
+        <is>
+          <t>Versalles</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>Vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="inlineStr">
+        <is>
+          <t>38401</t>
+        </is>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>Coacalco</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>38604</t>
+        </is>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>Cosmopol</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>43193</t>
+        </is>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>Cosmopol N1</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D92" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19" t="inlineStr">
+        <is>
+          <t>38894</t>
+        </is>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>Galerias Perinorte</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="inlineStr">
+        <is>
+          <t>38333</t>
+        </is>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>Izcalli Mega</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="19" t="inlineStr">
+        <is>
+          <t>38368</t>
+        </is>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
+        <is>
+          <t>Luna Park</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="19" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>Patio Ecatepec</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>38456</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>Plaza las Flores</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr">
+        <is>
+          <t>38339</t>
+        </is>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>38862</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>San Miguel Izcalli</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>Enrique Cesar Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>38186</t>
+        </is>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
+        <is>
+          <t>Arboledas</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D100" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>38230</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>ITEMS Edo de Mexico</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>38661</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>Jinetes</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>38674</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>Mundo E</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>38845</t>
+        </is>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>Mundo E II</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>38792</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>Pasaje Tlanepantla</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>38136</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>Punta Norte</t>
+        </is>
+      </c>
+      <c r="C106" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>38460</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>Santa Monica</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>38442</t>
+        </is>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>Sor Juana</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>38606</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>TlalnepantlaCarso</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr">
+        <is>
+          <t>38374</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>Valle Dorado</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>38694</t>
+        </is>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
+        <is>
+          <t>Villas de la Hacienda</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>Nancy Carolina Rodriguez Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>43194</t>
+        </is>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>Atana Lindavista</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="inlineStr">
+        <is>
+          <t>38527</t>
+        </is>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>Camarones</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D113" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E113" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="19" t="inlineStr">
+        <is>
+          <t>38837</t>
+        </is>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
+          <t>Centenario Azcapotzalco</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D114" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E114" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="19" t="inlineStr">
+        <is>
+          <t>38205</t>
+        </is>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
+          <t>Lindavista</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E115" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="19" t="inlineStr">
+        <is>
+          <t>38207</t>
+        </is>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
+        <is>
+          <t>Lindavista II</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D116" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E116" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>38371</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="inlineStr">
+        <is>
+          <t>Montevideo DT</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E117" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="inlineStr">
+        <is>
+          <t>43111</t>
+        </is>
+      </c>
+      <c r="B118" s="19" t="inlineStr">
+        <is>
+          <t>Montevideo Insurgentes</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D118" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E118" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="19" t="inlineStr">
+        <is>
+          <t>43195</t>
+        </is>
+      </c>
+      <c r="B119" s="19" t="inlineStr">
+        <is>
+          <t>Parque Jadin kiosko</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E119" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="inlineStr">
+        <is>
+          <t>38546</t>
+        </is>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>Patio Claveria</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D120" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E120" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>38677</t>
+        </is>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>Patio la Raza</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D121" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E121" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="19" t="inlineStr">
+        <is>
+          <t>43132</t>
+        </is>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Vista Norte</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D122" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E122" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t>38411</t>
+        </is>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>Torres Lindavista</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D123" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E123" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="inlineStr">
+        <is>
+          <t>38651</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="inlineStr">
+        <is>
+          <t>Via Vallejo</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D124" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>Vanessa Carreño Rios</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>38930</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="inlineStr">
+        <is>
+          <t>Blvd. Aeropuerto dt</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
+          <t>38529</t>
+        </is>
+      </c>
+      <c r="B126" s="19" t="inlineStr">
+        <is>
+          <t>Bosques de Aragon</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>38431</t>
+        </is>
+      </c>
+      <c r="B127" s="19" t="inlineStr">
+        <is>
+          <t>Eduardo Molina</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D127" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="19" t="inlineStr">
+        <is>
+          <t>38903</t>
+        </is>
+      </c>
+      <c r="B128" s="19" t="inlineStr">
+        <is>
+          <t>Encuentro Oceania</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D128" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="19" t="inlineStr">
+        <is>
+          <t>38995</t>
+        </is>
+      </c>
+      <c r="B129" s="19" t="inlineStr">
+        <is>
+          <t>Encuentro Oceania II</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
+          <t>38937</t>
+        </is>
+      </c>
+      <c r="B130" s="19" t="inlineStr">
+        <is>
+          <t>Parque Tepeyac Piso 1</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="19" t="inlineStr">
+        <is>
+          <t>38965</t>
+        </is>
+      </c>
+      <c r="B131" s="19" t="inlineStr">
+        <is>
+          <t>Parque Tepeyac Piso 2</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="19" t="inlineStr">
+        <is>
+          <t>38924</t>
+        </is>
+      </c>
+      <c r="B132" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Aeropuerto</t>
+        </is>
+      </c>
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D132" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t>38719</t>
+        </is>
+      </c>
+      <c r="B133" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Fortuna</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D133" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t>38811</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Tepeyac</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D134" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E134" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="19" t="inlineStr">
+        <is>
+          <t>38992</t>
+        </is>
+      </c>
+      <c r="B135" s="19" t="inlineStr">
+        <is>
+          <t>Tapo Puerta Oriente</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E135" s="19" t="inlineStr">
+        <is>
+          <t>Veronica Garcia Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="19" t="inlineStr">
+        <is>
+          <t>38695</t>
+        </is>
+      </c>
+      <c r="B136" s="19" t="inlineStr">
+        <is>
+          <t>Cetram 4 Caminos</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D136" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E136" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="19" t="inlineStr">
+        <is>
+          <t>38197</t>
+        </is>
+      </c>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t>Echegaray</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E137" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="19" t="inlineStr">
+        <is>
+          <t>38458</t>
+        </is>
+      </c>
+      <c r="B138" s="19" t="inlineStr">
+        <is>
+          <t>El Rosario</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D138" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E138" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="19" t="inlineStr">
+        <is>
+          <t>38770</t>
+        </is>
+      </c>
+      <c r="B139" s="19" t="inlineStr">
+        <is>
+          <t>Gustavo Baz 29</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E139" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="19" t="inlineStr">
+        <is>
+          <t>38561</t>
+        </is>
+      </c>
+      <c r="B140" s="19" t="inlineStr">
+        <is>
+          <t>Parque Toreo</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D140" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E140" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="19" t="inlineStr">
+        <is>
+          <t>38590</t>
+        </is>
+      </c>
+      <c r="B141" s="19" t="inlineStr">
+        <is>
+          <t>Parque Toreo II</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E141" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="19" t="inlineStr">
+        <is>
+          <t>38176</t>
+        </is>
+      </c>
+      <c r="B142" s="19" t="inlineStr">
+        <is>
+          <t>Periferico Satélite DT</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D142" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E142" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="19" t="inlineStr">
+        <is>
+          <t>38427</t>
+        </is>
+      </c>
+      <c r="B143" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Satelite</t>
+        </is>
+      </c>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D143" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E143" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="19" t="inlineStr">
+        <is>
+          <t>38859</t>
+        </is>
+      </c>
+      <c r="B144" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Satelite II N1</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D144" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E144" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="19" t="inlineStr">
+        <is>
+          <t>43152</t>
+        </is>
+      </c>
+      <c r="B145" s="19" t="inlineStr">
+        <is>
+          <t>Samara Satélite</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D145" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E145" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="19" t="inlineStr">
+        <is>
+          <t>38117</t>
+        </is>
+      </c>
+      <c r="B146" s="19" t="inlineStr">
+        <is>
+          <t>Satelite</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D146" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E146" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>38475</t>
+        </is>
+      </c>
+      <c r="B147" s="19" t="inlineStr">
+        <is>
+          <t>Satelite Centro Civico</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D147" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E147" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>38656</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="inlineStr">
+        <is>
+          <t>Viveros de la Loma</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D148" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E148" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Chabela Guadarrama</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t>43043</t>
+        </is>
+      </c>
+      <c r="B149" s="19" t="inlineStr">
+        <is>
+          <t>Atizapan</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D149" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E149" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="19" t="inlineStr">
+        <is>
+          <t>38149</t>
+        </is>
+      </c>
+      <c r="B150" s="19" t="inlineStr">
+        <is>
+          <t>Bellavista</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D150" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E150" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="19" t="inlineStr">
+        <is>
+          <t>38394</t>
+        </is>
+      </c>
+      <c r="B151" s="19" t="inlineStr">
+        <is>
+          <t>Centro Comercial Lomas Verdes</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D151" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E151" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t>38535</t>
+        </is>
+      </c>
+      <c r="B152" s="19" t="inlineStr">
+        <is>
+          <t>City Center Esmeralda</t>
+        </is>
+      </c>
+      <c r="C152" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D152" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E152" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="19" t="inlineStr">
+        <is>
+          <t>38507</t>
+        </is>
+      </c>
+      <c r="B153" s="19" t="inlineStr">
+        <is>
+          <t>Espacio Vista del Valle</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E153" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="19" t="inlineStr">
+        <is>
+          <t>38363</t>
+        </is>
+      </c>
+      <c r="B154" s="19" t="inlineStr">
+        <is>
+          <t>Galerias Atizapan</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="19" t="inlineStr">
+        <is>
+          <t>38119</t>
+        </is>
+      </c>
+      <c r="B155" s="19" t="inlineStr">
+        <is>
+          <t>Lomas Verdes</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D155" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="19" t="inlineStr">
+        <is>
+          <t>38270</t>
+        </is>
+      </c>
+      <c r="B156" s="19" t="inlineStr">
+        <is>
+          <t>Lomas Verdes II</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D156" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="19" t="inlineStr">
+        <is>
+          <t>38266</t>
+        </is>
+      </c>
+      <c r="B157" s="19" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D157" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="19" t="inlineStr">
+        <is>
+          <t>38925</t>
+        </is>
+      </c>
+      <c r="B158" s="19" t="inlineStr">
+        <is>
+          <t>Star Medica Lomas Verdes</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D158" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="19" t="inlineStr">
+        <is>
+          <t>43130</t>
+        </is>
+      </c>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>Town Center Nicolás Romero</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D159" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="19" t="inlineStr">
+        <is>
+          <t>38115</t>
+        </is>
+      </c>
+      <c r="B160" s="19" t="inlineStr">
+        <is>
+          <t>Zona Azul</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D160" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>38142</t>
+        </is>
+      </c>
+      <c r="B161" s="19" t="inlineStr">
+        <is>
+          <t>Zona Esmeralda</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="D161" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="19" t="inlineStr">
+        <is>
+          <t>38103</t>
+        </is>
+      </c>
+      <c r="B162" s="19" t="inlineStr">
+        <is>
+          <t>Aguilas</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D162" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E162" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>38746</t>
+        </is>
+      </c>
+      <c r="B163" s="19" t="inlineStr">
+        <is>
+          <t>Arcos Bosques II</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D163" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="19" t="inlineStr">
+        <is>
+          <t>38617</t>
+        </is>
+      </c>
+      <c r="B164" s="19" t="inlineStr">
+        <is>
+          <t>Axomiatla</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D164" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E164" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="19" t="inlineStr">
+        <is>
+          <t>38646</t>
+        </is>
+      </c>
+      <c r="B165" s="19" t="inlineStr">
+        <is>
+          <t>Carracci</t>
+        </is>
+      </c>
+      <c r="C165" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D165" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E165" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="19" t="inlineStr">
+        <is>
+          <t>38112</t>
+        </is>
+      </c>
+      <c r="B166" s="19" t="inlineStr">
+        <is>
+          <t>Insurgentes Parroquia</t>
+        </is>
+      </c>
+      <c r="C166" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D166" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E166" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="19" t="inlineStr">
+        <is>
+          <t>38227</t>
+        </is>
+      </c>
+      <c r="B167" s="19" t="inlineStr">
+        <is>
+          <t>Lomas Plaza</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D167" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="19" t="inlineStr">
+        <is>
+          <t>38730</t>
+        </is>
+      </c>
+      <c r="B168" s="19" t="inlineStr">
+        <is>
+          <t>Manacar PB</t>
+        </is>
+      </c>
+      <c r="C168" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D168" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E168" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="19" t="inlineStr">
+        <is>
+          <t>43142</t>
+        </is>
+      </c>
+      <c r="B169" s="19" t="inlineStr">
+        <is>
+          <t>Montes Urales</t>
+        </is>
+      </c>
+      <c r="C169" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D169" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E169" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="19" t="inlineStr">
+        <is>
+          <t>38188</t>
+        </is>
+      </c>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>Palmas</t>
+        </is>
+      </c>
+      <c r="C170" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D170" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E170" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="19" t="inlineStr">
+        <is>
+          <t>38692</t>
+        </is>
+      </c>
+      <c r="B171" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Exhibimex</t>
+        </is>
+      </c>
+      <c r="C171" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D171" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>38106</t>
+        </is>
+      </c>
+      <c r="B172" s="19" t="inlineStr">
+        <is>
+          <t>Prado Norte</t>
+        </is>
+      </c>
+      <c r="C172" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D172" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E172" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>38954</t>
+        </is>
+      </c>
+      <c r="B173" s="19" t="inlineStr">
+        <is>
+          <t>Universidad Anahuac Campus Sur</t>
+        </is>
+      </c>
+      <c r="C173" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D173" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>Adriana Alejandra Tanus Buhler</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>43011</t>
+        </is>
+      </c>
+      <c r="B174" s="19" t="inlineStr">
+        <is>
+          <t>Carr Toluca-Atlacomulco DT</t>
+        </is>
+      </c>
+      <c r="C174" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D174" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E174" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>43058</t>
+        </is>
+      </c>
+      <c r="B175" s="19" t="inlineStr">
+        <is>
+          <t>Casa de Gobierno DT</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D175" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>38847</t>
+        </is>
+      </c>
+      <c r="B176" s="19" t="inlineStr">
+        <is>
+          <t>El Molino</t>
+        </is>
+      </c>
+      <c r="C176" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D176" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="19" t="inlineStr">
+        <is>
+          <t>38578</t>
+        </is>
+      </c>
+      <c r="B177" s="19" t="inlineStr">
+        <is>
+          <t>Galerias Toluca</t>
+        </is>
+      </c>
+      <c r="C177" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D177" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="19" t="inlineStr">
+        <is>
+          <t>43147</t>
+        </is>
+      </c>
+      <c r="B178" s="19" t="inlineStr">
+        <is>
+          <t>Juarez 70</t>
+        </is>
+      </c>
+      <c r="C178" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D178" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E178" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="19" t="inlineStr">
+        <is>
+          <t>38829</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>Outlet Lerma</t>
+        </is>
+      </c>
+      <c r="C179" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D179" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="19" t="inlineStr">
+        <is>
+          <t>38769</t>
+        </is>
+      </c>
+      <c r="B180" s="19" t="inlineStr">
+        <is>
+          <t>Patio Toluca</t>
+        </is>
+      </c>
+      <c r="C180" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D180" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E180" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="19" t="inlineStr">
+        <is>
+          <t>38233</t>
+        </is>
+      </c>
+      <c r="B181" s="19" t="inlineStr">
+        <is>
+          <t>Toluca Colon</t>
+        </is>
+      </c>
+      <c r="C181" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D181" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>Andrea Nava Guzman</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="19" t="inlineStr">
+        <is>
+          <t>38439</t>
+        </is>
+      </c>
+      <c r="B182" s="19" t="inlineStr">
+        <is>
+          <t>Ángeles Interlomas</t>
+        </is>
+      </c>
+      <c r="C182" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D182" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="19" t="inlineStr">
+        <is>
+          <t>38568</t>
+        </is>
+      </c>
+      <c r="B183" s="19" t="inlineStr">
+        <is>
+          <t>Av Stim</t>
+        </is>
+      </c>
+      <c r="C183" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E183" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="19" t="inlineStr">
+        <is>
+          <t>38918</t>
+        </is>
+      </c>
+      <c r="B184" s="19" t="inlineStr">
+        <is>
+          <t>Bosque Real</t>
+        </is>
+      </c>
+      <c r="C184" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D184" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E184" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="19" t="inlineStr">
+        <is>
+          <t>38815</t>
+        </is>
+      </c>
+      <c r="B185" s="19" t="inlineStr">
+        <is>
+          <t>Central Interlomas</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E185" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="19" t="inlineStr">
+        <is>
+          <t>38126</t>
+        </is>
+      </c>
+      <c r="B186" s="19" t="inlineStr">
+        <is>
+          <t>Interlomas</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D186" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E186" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="19" t="inlineStr">
+        <is>
+          <t>38292</t>
+        </is>
+      </c>
+      <c r="B187" s="19" t="inlineStr">
+        <is>
+          <t>Jesús del Monte</t>
+        </is>
+      </c>
+      <c r="C187" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D187" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E187" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="19" t="inlineStr">
+        <is>
+          <t>38185</t>
+        </is>
+      </c>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>Magnocentro</t>
+        </is>
+      </c>
+      <c r="C188" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D188" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E188" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="19" t="inlineStr">
+        <is>
+          <t>43107</t>
+        </is>
+      </c>
+      <c r="B189" s="19" t="inlineStr">
+        <is>
+          <t>Pabellón Bosques</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D189" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E189" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="19" t="inlineStr">
+        <is>
+          <t>38452</t>
+        </is>
+      </c>
+      <c r="B190" s="19" t="inlineStr">
+        <is>
+          <t>Parque Interlomas</t>
+        </is>
+      </c>
+      <c r="C190" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D190" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E190" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="19" t="inlineStr">
+        <is>
+          <t>38466</t>
+        </is>
+      </c>
+      <c r="B191" s="19" t="inlineStr">
+        <is>
+          <t>Paseo Interlomas I</t>
+        </is>
+      </c>
+      <c r="C191" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D191" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E191" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="19" t="inlineStr">
+        <is>
+          <t>38553</t>
+        </is>
+      </c>
+      <c r="B192" s="19" t="inlineStr">
+        <is>
+          <t>Paseo Interlomas II</t>
+        </is>
+      </c>
+      <c r="C192" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D192" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E192" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="19" t="inlineStr">
+        <is>
+          <t>38799</t>
+        </is>
+      </c>
+      <c r="B193" s="19" t="inlineStr">
+        <is>
+          <t>Paseo Interlomas III</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D193" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E193" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="19" t="inlineStr">
+        <is>
+          <t>38179</t>
+        </is>
+      </c>
+      <c r="B194" s="19" t="inlineStr">
+        <is>
+          <t>Universidad Anáhuac</t>
+        </is>
+      </c>
+      <c r="C194" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D194" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E194" s="19" t="inlineStr">
+        <is>
+          <t>Areli Anahi Lazcano Lezama</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="19" t="inlineStr">
+        <is>
+          <t>38957</t>
+        </is>
+      </c>
+      <c r="B195" s="19" t="inlineStr">
+        <is>
+          <t>Avándaro</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D195" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E195" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="19" t="inlineStr">
+        <is>
+          <t>38547</t>
+        </is>
+      </c>
+      <c r="B196" s="19" t="inlineStr">
+        <is>
+          <t>Carr Toluca Mexico KM48</t>
+        </is>
+      </c>
+      <c r="C196" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D196" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E196" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="19" t="inlineStr">
+        <is>
+          <t>38138</t>
+        </is>
+      </c>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>Galerias metepec 1</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D197" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E197" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="19" t="inlineStr">
+        <is>
+          <t>43068</t>
+        </is>
+      </c>
+      <c r="B198" s="19" t="inlineStr">
+        <is>
+          <t>Galerias Metepec II</t>
+        </is>
+      </c>
+      <c r="C198" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D198" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E198" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="19" t="inlineStr">
+        <is>
+          <t>43059</t>
+        </is>
+      </c>
+      <c r="B199" s="19" t="inlineStr">
+        <is>
+          <t>La Providencia DT</t>
+        </is>
+      </c>
+      <c r="C199" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D199" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E199" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="19" t="inlineStr">
+        <is>
+          <t>38441</t>
+        </is>
+      </c>
+      <c r="B200" s="19" t="inlineStr">
+        <is>
+          <t>Metepec Plaza del Parque</t>
+        </is>
+      </c>
+      <c r="C200" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D200" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E200" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="19" t="inlineStr">
+        <is>
+          <t>38668</t>
+        </is>
+      </c>
+      <c r="B201" s="19" t="inlineStr">
+        <is>
+          <t>Pabellon Metepec</t>
+        </is>
+      </c>
+      <c r="C201" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D201" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E201" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="19" t="inlineStr">
+        <is>
+          <t>38896</t>
+        </is>
+      </c>
+      <c r="B202" s="19" t="inlineStr">
+        <is>
+          <t>Paseo Tollocan DT</t>
+        </is>
+      </c>
+      <c r="C202" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D202" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E202" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="19" t="inlineStr">
+        <is>
+          <t>38141</t>
+        </is>
+      </c>
+      <c r="B203" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Mayor Metepec</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D203" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E203" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="19" t="inlineStr">
+        <is>
+          <t>38987</t>
+        </is>
+      </c>
+      <c r="B204" s="19" t="inlineStr">
+        <is>
+          <t>Punta Zero Calimaya DT</t>
+        </is>
+      </c>
+      <c r="C204" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D204" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E204" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="19" t="inlineStr">
+        <is>
+          <t>38485</t>
+        </is>
+      </c>
+      <c r="B205" s="19" t="inlineStr">
+        <is>
+          <t>Sendero Toluca</t>
+        </is>
+      </c>
+      <c r="C205" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D205" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E205" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="19" t="inlineStr">
+        <is>
+          <t>38319</t>
+        </is>
+      </c>
+      <c r="B206" s="19" t="inlineStr">
+        <is>
+          <t>Tecnologico Metepec</t>
+        </is>
+      </c>
+      <c r="C206" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D206" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E206" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="19" t="inlineStr">
+        <is>
+          <t>38841</t>
+        </is>
+      </c>
+      <c r="B207" s="19" t="inlineStr">
+        <is>
+          <t>Townsquare Metepec</t>
+        </is>
+      </c>
+      <c r="C207" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D207" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E207" s="19" t="inlineStr">
+        <is>
+          <t>Daniel Flores Maldonado</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="19" t="inlineStr">
+        <is>
+          <t>38508</t>
+        </is>
+      </c>
+      <c r="B208" s="19" t="inlineStr">
+        <is>
+          <t>Ampliacion Santa Fe</t>
+        </is>
+      </c>
+      <c r="C208" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D208" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E208" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="19" t="inlineStr">
+        <is>
+          <t>38607</t>
+        </is>
+      </c>
+      <c r="B209" s="19" t="inlineStr">
+        <is>
+          <t>Carretera Mexico Toluca KM42</t>
+        </is>
+      </c>
+      <c r="C209" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D209" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E209" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="19" t="inlineStr">
+        <is>
+          <t>38633</t>
+        </is>
+      </c>
+      <c r="B210" s="19" t="inlineStr">
+        <is>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+        </is>
+      </c>
+      <c r="C210" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D210" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E210" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="19" t="inlineStr">
+        <is>
+          <t>38361</t>
+        </is>
+      </c>
+      <c r="B211" s="19" t="inlineStr">
+        <is>
+          <t>Castorena</t>
+        </is>
+      </c>
+      <c r="C211" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D211" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E211" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="19" t="inlineStr">
+        <is>
+          <t>38148</t>
+        </is>
+      </c>
+      <c r="B212" s="19" t="inlineStr">
+        <is>
+          <t>Centro Comercial Santa Fe 1</t>
+        </is>
+      </c>
+      <c r="C212" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D212" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E212" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="19" t="inlineStr">
+        <is>
+          <t>38225</t>
+        </is>
+      </c>
+      <c r="B213" s="19" t="inlineStr">
+        <is>
+          <t>Centro Comercial Santa Fe 2</t>
+        </is>
+      </c>
+      <c r="C213" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D213" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E213" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="19" t="inlineStr">
+        <is>
+          <t>38747</t>
+        </is>
+      </c>
+      <c r="B214" s="19" t="inlineStr">
+        <is>
+          <t>Centro Comercial Santa Fe 3</t>
+        </is>
+      </c>
+      <c r="C214" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D214" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E214" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="19" t="inlineStr">
+        <is>
+          <t>38438</t>
+        </is>
+      </c>
+      <c r="B215" s="19" t="inlineStr">
+        <is>
+          <t>City Walk</t>
+        </is>
+      </c>
+      <c r="C215" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D215" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E215" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="19" t="inlineStr">
+        <is>
+          <t>38704</t>
+        </is>
+      </c>
+      <c r="B216" s="19" t="inlineStr">
+        <is>
+          <t>Corportivo Banamex</t>
+        </is>
+      </c>
+      <c r="C216" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D216" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E216" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="19" t="inlineStr">
+        <is>
+          <t>38414</t>
+        </is>
+      </c>
+      <c r="B217" s="19" t="inlineStr">
+        <is>
+          <t>Park Plaza</t>
+        </is>
+      </c>
+      <c r="C217" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D217" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E217" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="19" t="inlineStr">
+        <is>
+          <t>38534</t>
+        </is>
+      </c>
+      <c r="B218" s="19" t="inlineStr">
+        <is>
+          <t>Patio Santa Fe 1</t>
+        </is>
+      </c>
+      <c r="C218" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D218" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E218" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="19" t="inlineStr">
+        <is>
+          <t>38749</t>
+        </is>
+      </c>
+      <c r="B219" s="19" t="inlineStr">
+        <is>
+          <t>Patio Santa Fe 2</t>
+        </is>
+      </c>
+      <c r="C219" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D219" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E219" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="19" t="inlineStr">
+        <is>
+          <t>38122</t>
+        </is>
+      </c>
+      <c r="B220" s="19" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="C220" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D220" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E220" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="19" t="inlineStr">
+        <is>
+          <t>38150</t>
+        </is>
+      </c>
+      <c r="B221" s="19" t="inlineStr">
+        <is>
+          <t>Santa Fe 2</t>
+        </is>
+      </c>
+      <c r="C221" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D221" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E221" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="19" t="inlineStr">
+        <is>
+          <t>38189</t>
+        </is>
+      </c>
+      <c r="B222" s="19" t="inlineStr">
+        <is>
+          <t>Santa Fe Imax</t>
+        </is>
+      </c>
+      <c r="C222" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D222" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E222" s="19" t="inlineStr">
+        <is>
+          <t>Erika Julieta Contreras Aguilera</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="19" t="inlineStr">
+        <is>
+          <t>38929</t>
+        </is>
+      </c>
+      <c r="B223" s="19" t="inlineStr">
+        <is>
+          <t>Aeropuerto Toluca AMB</t>
+        </is>
+      </c>
+      <c r="C223" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D223" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E223" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="19" t="inlineStr">
+        <is>
+          <t>43162</t>
+        </is>
+      </c>
+      <c r="B224" s="19" t="inlineStr">
+        <is>
+          <t>Apto Toluca SUE</t>
+        </is>
+      </c>
+      <c r="C224" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D224" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E224" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="19" t="inlineStr">
+        <is>
+          <t>38400</t>
+        </is>
+      </c>
+      <c r="B225" s="19" t="inlineStr">
+        <is>
+          <t>Centro Medico ABC Santa Fe</t>
+        </is>
+      </c>
+      <c r="C225" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D225" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E225" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="19" t="inlineStr">
+        <is>
+          <t>38798</t>
+        </is>
+      </c>
+      <c r="B226" s="19" t="inlineStr">
+        <is>
+          <t>Corp. Televisa Sta Fe</t>
+        </is>
+      </c>
+      <c r="C226" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D226" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E226" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="19" t="inlineStr">
+        <is>
+          <t>38755</t>
+        </is>
+      </c>
+      <c r="B227" s="19" t="inlineStr">
+        <is>
+          <t>Corporativo Santander</t>
+        </is>
+      </c>
+      <c r="C227" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D227" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E227" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="19" t="inlineStr">
+        <is>
+          <t>38512</t>
+        </is>
+      </c>
+      <c r="B228" s="19" t="inlineStr">
+        <is>
+          <t>Garden Santa Fe</t>
+        </is>
+      </c>
+      <c r="C228" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D228" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E228" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="19" t="inlineStr">
+        <is>
+          <t>38532</t>
+        </is>
+      </c>
+      <c r="B229" s="19" t="inlineStr">
+        <is>
+          <t>One o One</t>
+        </is>
+      </c>
+      <c r="C229" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D229" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E229" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="19" t="inlineStr">
+        <is>
+          <t>38777</t>
+        </is>
+      </c>
+      <c r="B230" s="19" t="inlineStr">
+        <is>
+          <t>Parque la Mexicana</t>
+        </is>
+      </c>
+      <c r="C230" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D230" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E230" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="19" t="inlineStr">
+        <is>
+          <t>38810</t>
+        </is>
+      </c>
+      <c r="B231" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Centenario ( Tenaria)</t>
+        </is>
+      </c>
+      <c r="C231" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D231" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E231" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="19" t="inlineStr">
+        <is>
+          <t>38158</t>
+        </is>
+      </c>
+      <c r="B232" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Lilas</t>
+        </is>
+      </c>
+      <c r="C232" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D232" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E232" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="19" t="inlineStr">
+        <is>
+          <t>38390</t>
+        </is>
+      </c>
+      <c r="B233" s="19" t="inlineStr">
+        <is>
+          <t>Samara I</t>
+        </is>
+      </c>
+      <c r="C233" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D233" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E233" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="19" t="inlineStr">
+        <is>
+          <t>38445</t>
+        </is>
+      </c>
+      <c r="B234" s="19" t="inlineStr">
+        <is>
+          <t>Samara II</t>
+        </is>
+      </c>
+      <c r="C234" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D234" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E234" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="19" t="inlineStr">
+        <is>
+          <t>38166</t>
+        </is>
+      </c>
+      <c r="B235" s="19" t="inlineStr">
+        <is>
+          <t>Superama SantaFe</t>
+        </is>
+      </c>
+      <c r="C235" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D235" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E235" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="19" t="inlineStr">
+        <is>
+          <t>38780</t>
+        </is>
+      </c>
+      <c r="B236" s="19" t="inlineStr">
+        <is>
+          <t>Tec Santa Fe</t>
+        </is>
+      </c>
+      <c r="C236" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D236" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E236" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="19" t="inlineStr">
+        <is>
+          <t>38751</t>
+        </is>
+      </c>
+      <c r="B237" s="19" t="inlineStr">
+        <is>
+          <t>Torre Zentrrum II</t>
+        </is>
+      </c>
+      <c r="C237" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D237" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E237" s="19" t="inlineStr">
+        <is>
+          <t>Jose De Jesus Magos Arzaluz</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="19" t="inlineStr">
+        <is>
+          <t>38715</t>
+        </is>
+      </c>
+      <c r="B238" s="19" t="inlineStr">
+        <is>
+          <t>Av. Coyoacan DT only</t>
+        </is>
+      </c>
+      <c r="C238" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D238" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E238" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="19" t="inlineStr">
+        <is>
+          <t>38372</t>
+        </is>
+      </c>
+      <c r="B239" s="19" t="inlineStr">
+        <is>
+          <t>Felix Cuevas</t>
+        </is>
+      </c>
+      <c r="C239" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D239" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E239" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="19" t="inlineStr">
+        <is>
+          <t>38549</t>
+        </is>
+      </c>
+      <c r="B240" s="19" t="inlineStr">
+        <is>
+          <t>Galerias Insurgentes</t>
+        </is>
+      </c>
+      <c r="C240" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D240" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E240" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="19" t="inlineStr">
+        <is>
+          <t>43105</t>
+        </is>
+      </c>
+      <c r="B241" s="19" t="inlineStr">
+        <is>
+          <t>Insurgentes Capital</t>
+        </is>
+      </c>
+      <c r="C241" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D241" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E241" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="19" t="inlineStr">
+        <is>
+          <t>38193</t>
+        </is>
+      </c>
+      <c r="B242" s="19" t="inlineStr">
+        <is>
+          <t>Metropoli Patriotismo</t>
+        </is>
+      </c>
+      <c r="C242" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D242" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E242" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="19" t="inlineStr">
+        <is>
+          <t>38416</t>
+        </is>
+      </c>
+      <c r="B243" s="19" t="inlineStr">
+        <is>
+          <t>Mixcoac</t>
+        </is>
+      </c>
+      <c r="C243" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D243" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E243" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="19" t="inlineStr">
+        <is>
+          <t>38530</t>
+        </is>
+      </c>
+      <c r="B244" s="19" t="inlineStr">
+        <is>
+          <t>Narvarte</t>
+        </is>
+      </c>
+      <c r="C244" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D244" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E244" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="19" t="inlineStr">
+        <is>
+          <t>38499</t>
+        </is>
+      </c>
+      <c r="B245" s="19" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C245" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D245" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E245" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="19" t="inlineStr">
+        <is>
+          <t>38587</t>
+        </is>
+      </c>
+      <c r="B246" s="19" t="inlineStr">
+        <is>
+          <t>Plateros</t>
+        </is>
+      </c>
+      <c r="C246" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D246" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E246" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="19" t="inlineStr">
+        <is>
+          <t>38764</t>
+        </is>
+      </c>
+      <c r="B247" s="19" t="inlineStr">
+        <is>
+          <t>Star Medica Napoles</t>
+        </is>
+      </c>
+      <c r="C247" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D247" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E247" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="19" t="inlineStr">
+        <is>
+          <t>38951</t>
+        </is>
+      </c>
+      <c r="B248" s="19" t="inlineStr">
+        <is>
+          <t>Universidad Panamericana</t>
+        </is>
+      </c>
+      <c r="C248" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D248" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E248" s="19" t="inlineStr">
+        <is>
+          <t>Juan Jesus Zuñiga Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="19" t="inlineStr">
+        <is>
+          <t>38717</t>
+        </is>
+      </c>
+      <c r="B249" s="19" t="inlineStr">
+        <is>
+          <t>Av Revolucion</t>
+        </is>
+      </c>
+      <c r="C249" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D249" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E249" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="19" t="inlineStr">
+        <is>
+          <t>38727</t>
+        </is>
+      </c>
+      <c r="B250" s="19" t="inlineStr">
+        <is>
+          <t>Centro Tk</t>
+        </is>
+      </c>
+      <c r="C250" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D250" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E250" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="19" t="inlineStr">
+        <is>
+          <t>38773</t>
+        </is>
+      </c>
+      <c r="B251" s="19" t="inlineStr">
+        <is>
+          <t>Colegio Americano</t>
+        </is>
+      </c>
+      <c r="C251" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D251" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E251" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="19" t="inlineStr">
+        <is>
+          <t>38709</t>
+        </is>
+      </c>
+      <c r="B252" s="19" t="inlineStr">
+        <is>
+          <t>Corporativo Barranca</t>
+        </is>
+      </c>
+      <c r="C252" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D252" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E252" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="19" t="inlineStr">
+        <is>
+          <t>38386</t>
+        </is>
+      </c>
+      <c r="B253" s="19" t="inlineStr">
+        <is>
+          <t>Duraznos</t>
+        </is>
+      </c>
+      <c r="C253" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D253" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E253" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="19" t="inlineStr">
+        <is>
+          <t>38461</t>
+        </is>
+      </c>
+      <c r="B254" s="19" t="inlineStr">
+        <is>
+          <t>Fuente de Tritones</t>
+        </is>
+      </c>
+      <c r="C254" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D254" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E254" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="19" t="inlineStr">
+        <is>
+          <t>38121</t>
+        </is>
+      </c>
+      <c r="B255" s="19" t="inlineStr">
+        <is>
+          <t>Herradura</t>
+        </is>
+      </c>
+      <c r="C255" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D255" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E255" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="19" t="inlineStr">
+        <is>
+          <t>38366</t>
+        </is>
+      </c>
+      <c r="B256" s="19" t="inlineStr">
+        <is>
+          <t>Hospital ABC</t>
+        </is>
+      </c>
+      <c r="C256" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D256" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E256" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="19" t="inlineStr">
+        <is>
+          <t>38538</t>
+        </is>
+      </c>
+      <c r="B257" s="19" t="inlineStr">
+        <is>
+          <t>Monte Pelvoux</t>
+        </is>
+      </c>
+      <c r="C257" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D257" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E257" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="19" t="inlineStr">
+        <is>
+          <t>43041</t>
+        </is>
+      </c>
+      <c r="B258" s="19" t="inlineStr">
+        <is>
+          <t>Parque Aztlan</t>
+        </is>
+      </c>
+      <c r="C258" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D258" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E258" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="19" t="inlineStr">
+        <is>
+          <t>38722</t>
+        </is>
+      </c>
+      <c r="B259" s="19" t="inlineStr">
+        <is>
+          <t>Patio Barranca N2</t>
+        </is>
+      </c>
+      <c r="C259" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D259" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E259" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="19" t="inlineStr">
+        <is>
+          <t>38720</t>
+        </is>
+      </c>
+      <c r="B260" s="19" t="inlineStr">
+        <is>
+          <t>Patio Barranca PB</t>
+        </is>
+      </c>
+      <c r="C260" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D260" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E260" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="19" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="B261" s="19" t="inlineStr">
+        <is>
+          <t>Torre Virreyes</t>
+        </is>
+      </c>
+      <c r="C261" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="D261" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E261" s="19" t="inlineStr">
+        <is>
+          <t>Manuel Alejandro Avila Molina</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="19" t="inlineStr">
+        <is>
+          <t>38419</t>
+        </is>
+      </c>
+      <c r="B262" s="19" t="inlineStr">
+        <is>
+          <t>Balbuena</t>
+        </is>
+      </c>
+      <c r="C262" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D262" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E262" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="19" t="inlineStr">
+        <is>
+          <t>38496</t>
+        </is>
+      </c>
+      <c r="B263" s="19" t="inlineStr">
+        <is>
+          <t>Casa Taxqueña</t>
+        </is>
+      </c>
+      <c r="C263" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D263" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E263" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="19" t="inlineStr">
+        <is>
+          <t>38611</t>
+        </is>
+      </c>
+      <c r="B264" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Basica</t>
+        </is>
+      </c>
+      <c r="C264" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D264" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E264" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="19" t="inlineStr">
+        <is>
+          <t>38645</t>
+        </is>
+      </c>
+      <c r="B265" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Central</t>
+        </is>
+      </c>
+      <c r="C265" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D265" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E265" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="19" t="inlineStr">
+        <is>
+          <t>38418</t>
+        </is>
+      </c>
+      <c r="B266" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Oriente l</t>
+        </is>
+      </c>
+      <c r="C266" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D266" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E266" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="19" t="inlineStr">
+        <is>
+          <t>38725</t>
+        </is>
+      </c>
+      <c r="B267" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Oriente ll</t>
+        </is>
+      </c>
+      <c r="C267" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D267" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E267" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="19" t="inlineStr">
+        <is>
+          <t>38468</t>
+        </is>
+      </c>
+      <c r="B268" s="19" t="inlineStr">
+        <is>
+          <t>Portal Churubusco</t>
+        </is>
+      </c>
+      <c r="C268" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D268" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E268" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="19" t="inlineStr">
+        <is>
+          <t>43070</t>
+        </is>
+      </c>
+      <c r="B269" s="19" t="inlineStr">
+        <is>
+          <t>Rojo Gomez DT</t>
+        </is>
+      </c>
+      <c r="C269" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D269" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E269" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="19" t="inlineStr">
+        <is>
+          <t>38289</t>
+        </is>
+      </c>
+      <c r="B270" s="19" t="inlineStr">
+        <is>
+          <t>Tezontle l</t>
+        </is>
+      </c>
+      <c r="C270" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D270" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E270" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="19" t="inlineStr">
+        <is>
+          <t>38279</t>
+        </is>
+      </c>
+      <c r="B271" s="19" t="inlineStr">
+        <is>
+          <t>Tezontle ll</t>
+        </is>
+      </c>
+      <c r="C271" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D271" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E271" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="19" t="inlineStr">
+        <is>
+          <t>38226</t>
+        </is>
+      </c>
+      <c r="B272" s="19" t="inlineStr">
+        <is>
+          <t>Via kiosko 515</t>
+        </is>
+      </c>
+      <c r="C272" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D272" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E272" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="19" t="inlineStr">
+        <is>
+          <t>38477</t>
+        </is>
+      </c>
+      <c r="B273" s="19" t="inlineStr">
+        <is>
+          <t>Zentralia churubusco</t>
+        </is>
+      </c>
+      <c r="C273" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D273" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E273" s="19" t="inlineStr">
+        <is>
+          <t>Ariana Janet Gutierrez Martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="19" t="inlineStr">
+        <is>
+          <t>38169</t>
+        </is>
+      </c>
+      <c r="B274" s="19" t="inlineStr">
+        <is>
+          <t>Altavista</t>
+        </is>
+      </c>
+      <c r="C274" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D274" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E274" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="19" t="inlineStr">
+        <is>
+          <t>38615</t>
+        </is>
+      </c>
+      <c r="B275" s="19" t="inlineStr">
+        <is>
+          <t>Grand San Jeronimo</t>
+        </is>
+      </c>
+      <c r="C275" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D275" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E275" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="19" t="inlineStr">
+        <is>
+          <t>38447</t>
+        </is>
+      </c>
+      <c r="B276" s="19" t="inlineStr">
+        <is>
+          <t>Hospital Angeles del Pedregal</t>
+        </is>
+      </c>
+      <c r="C276" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D276" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E276" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="19" t="inlineStr">
+        <is>
+          <t>43159</t>
+        </is>
+      </c>
+      <c r="B277" s="19" t="inlineStr">
+        <is>
+          <t>Hospital Angeles del Pedregal II</t>
+        </is>
+      </c>
+      <c r="C277" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D277" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E277" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="19" t="inlineStr">
+        <is>
+          <t>38428</t>
+        </is>
+      </c>
+      <c r="B278" s="19" t="inlineStr">
+        <is>
+          <t>Jardines del Pedregal</t>
+        </is>
+      </c>
+      <c r="C278" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D278" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E278" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="19" t="inlineStr">
+        <is>
+          <t>38571</t>
+        </is>
+      </c>
+      <c r="B279" s="19" t="inlineStr">
+        <is>
+          <t>Jolie Place</t>
+        </is>
+      </c>
+      <c r="C279" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D279" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E279" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="19" t="inlineStr">
+        <is>
+          <t>38398</t>
+        </is>
+      </c>
+      <c r="B280" s="19" t="inlineStr">
+        <is>
+          <t>Mexfund Pedregal</t>
+        </is>
+      </c>
+      <c r="C280" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D280" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E280" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="19" t="inlineStr">
+        <is>
+          <t>38580</t>
+        </is>
+      </c>
+      <c r="B281" s="19" t="inlineStr">
+        <is>
+          <t>Pasaje San Jeronimo</t>
+        </is>
+      </c>
+      <c r="C281" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D281" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E281" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="19" t="inlineStr">
+        <is>
+          <t>38691</t>
+        </is>
+      </c>
+      <c r="B282" s="19" t="inlineStr">
+        <is>
+          <t>Patio Revolución</t>
+        </is>
+      </c>
+      <c r="C282" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D282" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E282" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="19" t="inlineStr">
+        <is>
+          <t>38107</t>
+        </is>
+      </c>
+      <c r="B283" s="19" t="inlineStr">
+        <is>
+          <t>Pedregal</t>
+        </is>
+      </c>
+      <c r="C283" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D283" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E283" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="19" t="inlineStr">
+        <is>
+          <t>38544</t>
+        </is>
+      </c>
+      <c r="B284" s="19" t="inlineStr">
+        <is>
+          <t>Picacho Ajusco</t>
+        </is>
+      </c>
+      <c r="C284" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D284" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E284" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="19" t="inlineStr">
+        <is>
+          <t>38129</t>
+        </is>
+      </c>
+      <c r="B285" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Santa Teresa</t>
+        </is>
+      </c>
+      <c r="C285" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D285" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E285" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="19" t="inlineStr">
+        <is>
+          <t>38124</t>
+        </is>
+      </c>
+      <c r="B286" s="19" t="inlineStr">
+        <is>
+          <t>San Jeronimo</t>
+        </is>
+      </c>
+      <c r="C286" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D286" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E286" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="19" t="inlineStr">
+        <is>
+          <t>38116</t>
+        </is>
+      </c>
+      <c r="B287" s="19" t="inlineStr">
+        <is>
+          <t>Santa Teresa</t>
+        </is>
+      </c>
+      <c r="C287" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D287" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E287" s="19" t="inlineStr">
+        <is>
+          <t>Cesar Alfonso Castillo Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="19" t="inlineStr">
+        <is>
+          <t>38471</t>
+        </is>
+      </c>
+      <c r="B288" s="19" t="inlineStr">
+        <is>
+          <t>Angeles Acoxpa</t>
+        </is>
+      </c>
+      <c r="C288" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D288" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E288" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="19" t="inlineStr">
+        <is>
+          <t>38964</t>
+        </is>
+      </c>
+      <c r="B289" s="19" t="inlineStr">
+        <is>
+          <t>Biblioteca Tec</t>
+        </is>
+      </c>
+      <c r="C289" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D289" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E289" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="19" t="inlineStr">
+        <is>
+          <t>38367</t>
+        </is>
+      </c>
+      <c r="B290" s="19" t="inlineStr">
+        <is>
+          <t>CM Coapa</t>
+        </is>
+      </c>
+      <c r="C290" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D290" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E290" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="19" t="inlineStr">
+        <is>
+          <t>38393</t>
+        </is>
+      </c>
+      <c r="B291" s="19" t="inlineStr">
+        <is>
+          <t>Coapa Chedraui</t>
+        </is>
+      </c>
+      <c r="C291" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D291" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E291" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="19" t="inlineStr">
+        <is>
+          <t>38469</t>
+        </is>
+      </c>
+      <c r="B292" s="19" t="inlineStr">
+        <is>
+          <t>Galerias Coapa</t>
+        </is>
+      </c>
+      <c r="C292" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D292" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E292" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="19" t="inlineStr">
+        <is>
+          <t>38114</t>
+        </is>
+      </c>
+      <c r="B293" s="19" t="inlineStr">
+        <is>
+          <t>Miramontes</t>
+        </is>
+      </c>
+      <c r="C293" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D293" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E293" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="19" t="inlineStr">
+        <is>
+          <t>38494</t>
+        </is>
+      </c>
+      <c r="B294" s="19" t="inlineStr">
+        <is>
+          <t>Pabellon Cuemanco</t>
+        </is>
+      </c>
+      <c r="C294" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D294" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E294" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="19" t="inlineStr">
+        <is>
+          <t>38472</t>
+        </is>
+      </c>
+      <c r="B295" s="19" t="inlineStr">
+        <is>
+          <t>Plaza America DT</t>
+        </is>
+      </c>
+      <c r="C295" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D295" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E295" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="19" t="inlineStr">
+        <is>
+          <t>38360</t>
+        </is>
+      </c>
+      <c r="B296" s="19" t="inlineStr">
+        <is>
+          <t>Plaza la Hacienda</t>
+        </is>
+      </c>
+      <c r="C296" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D296" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E296" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="19" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="B297" s="19" t="inlineStr">
+        <is>
+          <t>Tec de Monterrey CCM</t>
+        </is>
+      </c>
+      <c r="C297" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D297" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E297" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="19" t="inlineStr">
+        <is>
+          <t>38637</t>
+        </is>
+      </c>
+      <c r="B298" s="19" t="inlineStr">
+        <is>
+          <t>Tlalpan Nativitas</t>
+        </is>
+      </c>
+      <c r="C298" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D298" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E298" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="19" t="inlineStr">
+        <is>
+          <t>38379</t>
+        </is>
+      </c>
+      <c r="B299" s="19" t="inlineStr">
+        <is>
+          <t>Via Acoxpa</t>
+        </is>
+      </c>
+      <c r="C299" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D299" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E299" s="19" t="inlineStr">
+        <is>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="19" t="inlineStr">
+        <is>
+          <t>38784</t>
+        </is>
+      </c>
+      <c r="B300" s="19" t="inlineStr">
+        <is>
+          <t>Artz Pedregal PB CC</t>
+        </is>
+      </c>
+      <c r="C300" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D300" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E300" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="19" t="inlineStr">
+        <is>
+          <t>38791</t>
+        </is>
+      </c>
+      <c r="B301" s="19" t="inlineStr">
+        <is>
+          <t>Artz Pedregal Reserve</t>
+        </is>
+      </c>
+      <c r="C301" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D301" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E301" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="19" t="inlineStr">
+        <is>
+          <t>38172</t>
+        </is>
+      </c>
+      <c r="B302" s="19" t="inlineStr">
+        <is>
+          <t>Gran Sur</t>
+        </is>
+      </c>
+      <c r="C302" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D302" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E302" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="19" t="inlineStr">
+        <is>
+          <t>38406</t>
+        </is>
+      </c>
+      <c r="B303" s="19" t="inlineStr">
+        <is>
+          <t>Medica Sur</t>
+        </is>
+      </c>
+      <c r="C303" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D303" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E303" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="19" t="inlineStr">
+        <is>
+          <t>38806</t>
+        </is>
+      </c>
+      <c r="B304" s="19" t="inlineStr">
+        <is>
+          <t>Patio Tlalpan</t>
+        </is>
+      </c>
+      <c r="C304" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D304" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E304" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="19" t="inlineStr">
+        <is>
+          <t>38402</t>
+        </is>
+      </c>
+      <c r="B305" s="19" t="inlineStr">
+        <is>
+          <t>PeriSur</t>
+        </is>
+      </c>
+      <c r="C305" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D305" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E305" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="19" t="inlineStr">
+        <is>
+          <t>38866</t>
+        </is>
+      </c>
+      <c r="B306" s="19" t="inlineStr">
+        <is>
+          <t>Perisur Reserve</t>
+        </is>
+      </c>
+      <c r="C306" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D306" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E306" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="19" t="inlineStr">
+        <is>
+          <t>38605</t>
+        </is>
+      </c>
+      <c r="B307" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Cuicuilco</t>
+        </is>
+      </c>
+      <c r="C307" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D307" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E307" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="19" t="inlineStr">
+        <is>
+          <t>38560</t>
+        </is>
+      </c>
+      <c r="B308" s="19" t="inlineStr">
+        <is>
+          <t>Renato Leduc</t>
+        </is>
+      </c>
+      <c r="C308" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D308" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E308" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="19" t="inlineStr">
+        <is>
+          <t>38131</t>
+        </is>
+      </c>
+      <c r="B309" s="19" t="inlineStr">
+        <is>
+          <t>Tepepan</t>
+        </is>
+      </c>
+      <c r="C309" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D309" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E309" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="19" t="inlineStr">
+        <is>
+          <t>38625</t>
+        </is>
+      </c>
+      <c r="B310" s="19" t="inlineStr">
+        <is>
+          <t>Tezoquipa</t>
+        </is>
+      </c>
+      <c r="C310" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D310" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E310" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="19" t="inlineStr">
+        <is>
+          <t>38543</t>
+        </is>
+      </c>
+      <c r="B311" s="19" t="inlineStr">
+        <is>
+          <t>Tlalpan Hospitales</t>
+        </is>
+      </c>
+      <c r="C311" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D311" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E311" s="19" t="inlineStr">
+        <is>
+          <t>Hazar Susim Trejo Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="19" t="inlineStr">
+        <is>
+          <t>38663</t>
+        </is>
+      </c>
+      <c r="B312" s="19" t="inlineStr">
+        <is>
+          <t>Copilco 20</t>
+        </is>
+      </c>
+      <c r="C312" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D312" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E312" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="19" t="inlineStr">
+        <is>
+          <t>38365</t>
+        </is>
+      </c>
+      <c r="B313" s="19" t="inlineStr">
+        <is>
+          <t>Coyoacan Centro</t>
+        </is>
+      </c>
+      <c r="C313" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D313" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E313" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="19" t="inlineStr">
+        <is>
+          <t>38484</t>
+        </is>
+      </c>
+      <c r="B314" s="19" t="inlineStr">
+        <is>
+          <t>Gandhi</t>
+        </is>
+      </c>
+      <c r="C314" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D314" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E314" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="19" t="inlineStr">
+        <is>
+          <t>38152</t>
+        </is>
+      </c>
+      <c r="B315" s="19" t="inlineStr">
+        <is>
+          <t>Insurgentes Relox</t>
+        </is>
+      </c>
+      <c r="C315" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D315" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E315" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="19" t="inlineStr">
+        <is>
+          <t>38113</t>
+        </is>
+      </c>
+      <c r="B316" s="19" t="inlineStr">
+        <is>
+          <t>Juan Pablo II</t>
+        </is>
+      </c>
+      <c r="C316" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D316" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E316" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="19" t="inlineStr">
+        <is>
+          <t>38208</t>
+        </is>
+      </c>
+      <c r="B317" s="19" t="inlineStr">
+        <is>
+          <t>Miguel Angel de Quevedo II</t>
+        </is>
+      </c>
+      <c r="C317" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D317" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E317" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="19" t="inlineStr">
+        <is>
+          <t>38239</t>
+        </is>
+      </c>
+      <c r="B318" s="19" t="inlineStr">
+        <is>
+          <t>Miguel Angel de Quevedo III</t>
+        </is>
+      </c>
+      <c r="C318" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D318" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E318" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="19" t="inlineStr">
+        <is>
+          <t>38620</t>
+        </is>
+      </c>
+      <c r="B319" s="19" t="inlineStr">
+        <is>
+          <t>Oasis I</t>
+        </is>
+      </c>
+      <c r="C319" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D319" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E319" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="19" t="inlineStr">
+        <is>
+          <t>38585</t>
+        </is>
+      </c>
+      <c r="B320" s="19" t="inlineStr">
+        <is>
+          <t>Oasis II</t>
+        </is>
+      </c>
+      <c r="C320" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D320" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E320" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="19" t="inlineStr">
+        <is>
+          <t>38139</t>
+        </is>
+      </c>
+      <c r="B321" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Inn</t>
+        </is>
+      </c>
+      <c r="C321" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D321" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E321" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="19" t="inlineStr">
+        <is>
+          <t>38430</t>
+        </is>
+      </c>
+      <c r="B322" s="19" t="inlineStr">
+        <is>
+          <t>Prisma Insurgentes</t>
+        </is>
+      </c>
+      <c r="C322" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D322" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E322" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="19" t="inlineStr">
+        <is>
+          <t>43025</t>
+        </is>
+      </c>
+      <c r="B323" s="19" t="inlineStr">
+        <is>
+          <t>Punto MAQ</t>
+        </is>
+      </c>
+      <c r="C323" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D323" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E323" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="19" t="inlineStr">
+        <is>
+          <t>38417</t>
+        </is>
+      </c>
+      <c r="B324" s="19" t="inlineStr">
+        <is>
+          <t>San Jose Insurgentes</t>
+        </is>
+      </c>
+      <c r="C324" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D324" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E324" s="19" t="inlineStr">
+        <is>
+          <t>Jaqueline Cortes Ayala</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="19" t="inlineStr">
+        <is>
+          <t>38800</t>
+        </is>
+      </c>
+      <c r="B325" s="19" t="inlineStr">
+        <is>
+          <t>Antenas PA</t>
+        </is>
+      </c>
+      <c r="C325" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D325" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E325" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="19" t="inlineStr">
+        <is>
+          <t>38801</t>
+        </is>
+      </c>
+      <c r="B326" s="19" t="inlineStr">
+        <is>
+          <t>Antenas PB</t>
+        </is>
+      </c>
+      <c r="C326" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D326" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E326" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="19" t="inlineStr">
+        <is>
+          <t>43163</t>
+        </is>
+      </c>
+      <c r="B327" s="19" t="inlineStr">
+        <is>
+          <t>Av. México Ixtapaluca</t>
+        </is>
+      </c>
+      <c r="C327" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D327" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E327" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="19" t="inlineStr">
+        <is>
+          <t>38594</t>
+        </is>
+      </c>
+      <c r="B328" s="19" t="inlineStr">
+        <is>
+          <t>Carretera Mexico Puebla</t>
+        </is>
+      </c>
+      <c r="C328" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D328" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E328" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="19" t="inlineStr">
+        <is>
+          <t>38657</t>
+        </is>
+      </c>
+      <c r="B329" s="19" t="inlineStr">
+        <is>
+          <t>Patio Lomas Estrella</t>
+        </is>
+      </c>
+      <c r="C329" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D329" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E329" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="19" t="inlineStr">
+        <is>
+          <t>43026</t>
+        </is>
+      </c>
+      <c r="B330" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Ermita</t>
+        </is>
+      </c>
+      <c r="C330" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D330" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E330" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="19" t="inlineStr">
+        <is>
+          <t>43169</t>
+        </is>
+      </c>
+      <c r="B331" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Tepozán</t>
+        </is>
+      </c>
+      <c r="C331" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D331" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E331" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="19" t="inlineStr">
+        <is>
+          <t>38855</t>
+        </is>
+      </c>
+      <c r="B332" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Zapotitlán DT</t>
+        </is>
+      </c>
+      <c r="C332" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D332" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E332" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="19" t="inlineStr">
+        <is>
+          <t>38502</t>
+        </is>
+      </c>
+      <c r="B333" s="19" t="inlineStr">
+        <is>
+          <t>San Marcos DT</t>
+        </is>
+      </c>
+      <c r="C333" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D333" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E333" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="19" t="inlineStr">
+        <is>
+          <t>38659</t>
+        </is>
+      </c>
+      <c r="B334" s="19" t="inlineStr">
+        <is>
+          <t>Sendero Ixtapaluca</t>
+        </is>
+      </c>
+      <c r="C334" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D334" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E334" s="19" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Elguera Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="19" t="inlineStr">
+        <is>
+          <t>38619</t>
+        </is>
+      </c>
+      <c r="B335" s="19" t="inlineStr">
+        <is>
+          <t>Calzada de Tlalpan</t>
+        </is>
+      </c>
+      <c r="C335" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D335" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E335" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="19" t="inlineStr">
+        <is>
+          <t>38526</t>
+        </is>
+      </c>
+      <c r="B336" s="19" t="inlineStr">
+        <is>
+          <t>City Shops Del Valle</t>
+        </is>
+      </c>
+      <c r="C336" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D336" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E336" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="19" t="inlineStr">
+        <is>
+          <t>38464</t>
+        </is>
+      </c>
+      <c r="B337" s="19" t="inlineStr">
+        <is>
+          <t>Corporativo Coyoacan</t>
+        </is>
+      </c>
+      <c r="C337" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D337" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E337" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="19" t="inlineStr">
+        <is>
+          <t>38340</t>
+        </is>
+      </c>
+      <c r="B338" s="19" t="inlineStr">
+        <is>
+          <t>Division del Norte</t>
+        </is>
+      </c>
+      <c r="C338" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D338" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E338" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="19" t="inlineStr">
+        <is>
+          <t>38579</t>
+        </is>
+      </c>
+      <c r="B339" s="19" t="inlineStr">
+        <is>
+          <t>Division del Norte II</t>
+        </is>
+      </c>
+      <c r="C339" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D339" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E339" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="19" t="inlineStr">
+        <is>
+          <t>38888</t>
+        </is>
+      </c>
+      <c r="B340" s="19" t="inlineStr">
+        <is>
+          <t>Mitikah</t>
+        </is>
+      </c>
+      <c r="C340" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D340" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E340" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="19" t="inlineStr">
+        <is>
+          <t>38941</t>
+        </is>
+      </c>
+      <c r="B341" s="19" t="inlineStr">
+        <is>
+          <t>Mitikah Restaurantes</t>
+        </is>
+      </c>
+      <c r="C341" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D341" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E341" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="19" t="inlineStr">
+        <is>
+          <t>38501</t>
+        </is>
+      </c>
+      <c r="B342" s="19" t="inlineStr">
+        <is>
+          <t>Patio Universidad</t>
+        </is>
+      </c>
+      <c r="C342" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D342" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E342" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="19" t="inlineStr">
+        <is>
+          <t>38482</t>
+        </is>
+      </c>
+      <c r="B343" s="19" t="inlineStr">
+        <is>
+          <t>Pestalozzi</t>
+        </is>
+      </c>
+      <c r="C343" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D343" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E343" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="19" t="inlineStr">
+        <is>
+          <t>38134</t>
+        </is>
+      </c>
+      <c r="B344" s="19" t="inlineStr">
+        <is>
+          <t>Pilares</t>
+        </is>
+      </c>
+      <c r="C344" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D344" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E344" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="19" t="inlineStr">
+        <is>
+          <t>38569</t>
+        </is>
+      </c>
+      <c r="B345" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Universidad</t>
+        </is>
+      </c>
+      <c r="C345" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D345" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E345" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="19" t="inlineStr">
+        <is>
+          <t>38513</t>
+        </is>
+      </c>
+      <c r="B346" s="19" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C346" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D346" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E346" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="19" t="inlineStr">
+        <is>
+          <t>38260</t>
+        </is>
+      </c>
+      <c r="B347" s="19" t="inlineStr">
+        <is>
+          <t>Tlacoquemecatl</t>
+        </is>
+      </c>
+      <c r="C347" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D347" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E347" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="19" t="inlineStr">
+        <is>
+          <t>38570</t>
+        </is>
+      </c>
+      <c r="B348" s="19" t="inlineStr">
+        <is>
+          <t>Universidad 767</t>
+        </is>
+      </c>
+      <c r="C348" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D348" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E348" s="19" t="inlineStr">
+        <is>
+          <t>Luis Alberto Quevedo Rodriguez</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="19" t="inlineStr">
+        <is>
+          <t>38375</t>
+        </is>
+      </c>
+      <c r="B349" s="19" t="inlineStr">
+        <is>
+          <t>Americas Ecatepec</t>
+        </is>
+      </c>
+      <c r="C349" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D349" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E349" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="19" t="inlineStr">
+        <is>
+          <t>38567</t>
+        </is>
+      </c>
+      <c r="B350" s="19" t="inlineStr">
+        <is>
+          <t>Aragon II</t>
+        </is>
+      </c>
+      <c r="C350" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D350" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E350" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="19" t="inlineStr">
+        <is>
+          <t>43164</t>
+        </is>
+      </c>
+      <c r="B351" s="19" t="inlineStr">
+        <is>
+          <t>Blvd Ojo de Agua DT</t>
+        </is>
+      </c>
+      <c r="C351" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D351" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E351" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="19" t="inlineStr">
+        <is>
+          <t>38351</t>
+        </is>
+      </c>
+      <c r="B352" s="19" t="inlineStr">
+        <is>
+          <t>Ciudad Jardin l</t>
+        </is>
+      </c>
+      <c r="C352" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D352" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E352" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="19" t="inlineStr">
+        <is>
+          <t>38511</t>
+        </is>
+      </c>
+      <c r="B353" s="19" t="inlineStr">
+        <is>
+          <t>Ciudad Jardin ll</t>
+        </is>
+      </c>
+      <c r="C353" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D353" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E353" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="19" t="inlineStr">
+        <is>
+          <t>43034</t>
+        </is>
+      </c>
+      <c r="B354" s="19" t="inlineStr">
+        <is>
+          <t>Macroplaza Tecamac</t>
+        </is>
+      </c>
+      <c r="C354" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D354" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E354" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="19" t="inlineStr">
+        <is>
+          <t>38716</t>
+        </is>
+      </c>
+      <c r="B355" s="19" t="inlineStr">
+        <is>
+          <t>Multiplaza Bosques</t>
+        </is>
+      </c>
+      <c r="C355" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D355" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E355" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="19" t="inlineStr">
+        <is>
+          <t>38718</t>
+        </is>
+      </c>
+      <c r="B356" s="19" t="inlineStr">
+        <is>
+          <t>Paseo Ventura</t>
+        </is>
+      </c>
+      <c r="C356" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D356" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E356" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="19" t="inlineStr">
+        <is>
+          <t>38429</t>
+        </is>
+      </c>
+      <c r="B357" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Aragon</t>
+        </is>
+      </c>
+      <c r="C357" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D357" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E357" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="19" t="inlineStr">
+        <is>
+          <t>38684</t>
+        </is>
+      </c>
+      <c r="B358" s="19" t="inlineStr">
+        <is>
+          <t>Plaza Chimalhuacan</t>
+        </is>
+      </c>
+      <c r="C358" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D358" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E358" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="19" t="inlineStr">
+        <is>
+          <t>38678</t>
+        </is>
+      </c>
+      <c r="B359" s="19" t="inlineStr">
+        <is>
+          <t>Power Center las Americas</t>
+        </is>
+      </c>
+      <c r="C359" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D359" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E359" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="19" t="inlineStr">
+        <is>
+          <t>43183</t>
+        </is>
+      </c>
+      <c r="B360" s="19" t="inlineStr">
+        <is>
+          <t>Puerta Texcoco</t>
+        </is>
+      </c>
+      <c r="C360" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D360" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E360" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="19" t="inlineStr">
+        <is>
+          <t>38996</t>
+        </is>
+      </c>
+      <c r="B361" s="19" t="inlineStr">
+        <is>
+          <t>Valle de Aragon</t>
+        </is>
+      </c>
+      <c r="C361" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="D361" s="19" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="E361" s="19" t="inlineStr">
+        <is>
+          <t>Monica Selene Morales Ibarra</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E361"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3154,12 +12881,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sin columna Estatus, se incluyen todas las tiendas del Directorio</t>
+          <t>Aplicar el filtro de estatus definido en includedStoreStatuses</t>
         </is>
       </c>
     </row>
@@ -3262,6 +12989,23 @@
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Fotografía institucional del Director Regional</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>includedStoreStatuses</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Único estatus incluido en tiendas, conteos y avance</t>
         </is>
       </c>
     </row>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gerentes'!$A$4:$F$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tiendas Abiertas'!$A$4:$E$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Organigrama'!$A$4:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tiendas Abiertas'!$A$4:$E$361</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -84,8 +86,14 @@
       <color rgb="0036574D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="005C4A00"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +155,11 @@
         <fgColor rgb="00F4F8F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2BF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -184,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,6 +234,7 @@
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3050,6 +3064,9 @@
     <cfRule type="expression" priority="6" dxfId="2">
       <formula>E5="Pendiente"</formula>
     </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>E5="Pendiente"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="F5:F104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -3072,6 +3089,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>CMS · Organigrama Región | Centro's</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
+      <c r="G1" s="14" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Edita nombre, rol, foto y Activo. Python publica únicamente las filas con Activo = Si.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Rol</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Foto WebP</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Centro's</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Raúl Sierra</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Director Starbucks México</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>assets/director/raul-sierra.webp</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Centro Centro</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Oliver Roberto Perez Briones</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Director Regional</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Centro Poniente</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Jorge Farrera Pinal</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Director Regional</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Centro Sur</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Cielo Aide Morera Urrego</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Director Regional</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Centro Norte</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Jorge Antonio Alcantar Aguiar</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Director Regional</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>assets/director/jorge-alcantar.webp</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Si,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12776,7 +13036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -2109,11 +2109,6 @@
           <t>CMS · Gerentes de Distrito</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
@@ -2122,7 +2117,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -3107,12 +3101,6 @@
           <t>CMS · Organigrama Región | Centro's</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
-      <c r="G1" s="14" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
@@ -3169,7 +3157,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>Raúl Sierra</t>
+          <t>Raúl Sinohe Sierra Santa Maria</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -3348,10 +3336,6 @@
           <t>CMS · Tiendas Abiertas</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
@@ -13064,7 +13048,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="Re1d00d2790db4049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R353984ff68214648"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="Rcb5f81fef29940aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="R7911340ac0484b4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="Rd2166c6cfc4f4595"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="R5b20b5b9cc644815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R1f7a128eb2094d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R6a8503de95834d7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="R4eb00b01f3024b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="R5b587cf49a5c4a51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -85,8 +85,13 @@
       <x:color rgb="FF5C4A00"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -153,6 +158,16 @@
         <x:fgColor rgb="FFFFF2BF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F3ED"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -179,7 +194,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyAlignment="1">
@@ -217,6 +232,15 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -2053,7 +2077,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4adb0da55054655"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8623b679093f42fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3073,7 +3097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad979debe4564e58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R401edeaeefb54ac3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13244,6 +13268,18 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="23" t="str">
+        <x:v>ignoredResponseIds</x:v>
+      </x:c>
+      <x:c r="B16" s="23" t="str">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="str">
+        <x:v>Ids originales de Forms excluidos temporalmente como pruebas; no bloquea respuestas reales del CeCo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="8" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:C1"/>
@@ -13256,7 +13292,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98ff2c42ddbf49b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89f4b4c369fb45a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/cms/Sistema_Evidencias_OPS_CMS.xlsx
+++ b/cms/Sistema_Evidencias_OPS_CMS.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="Rd69528b13f0345a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R4db4c06ffd8f4693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R6e800e54c4db4aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="Rfa197e560a5e4679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="Re4ae619cd6a945cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="1" r:id="R0573a88a9a2a4493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gerentes" sheetId="2" r:id="R7abd3811458a4709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organigrama" sheetId="3" r:id="R05be1645096345a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas Abiertas" sheetId="4" r:id="Rcd17933bbb8b4bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion" sheetId="5" r:id="R0a11951dfa5844ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2077,7 +2077,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1af1cb86d0b4ae2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80e3dfc694354c53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3097,7 +3097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfd5e23ca7504bef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d16f6df4b974957"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13267,15 +13267,9 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="23" t="str">
-        <x:v>ignoredResponseIds</x:v>
-      </x:c>
-      <x:c r="B16" s="23" t="str">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="str">
-        <x:v>Ids originales de Forms excluidos temporalmente como pruebas; no bloquea respuestas reales del CeCo</x:v>
-      </x:c>
+      <x:c r="A16" s="23"/>
+      <x:c r="B16" s="23"/>
+      <x:c r="C16" s="27"/>
     </x:row>
     <x:row r="17" ht="8" customHeight="1"/>
   </x:sheetData>
@@ -13290,7 +13284,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fe6a9c4613247c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79b1cd2b8dbf4bbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>